--- a/reports/module-migration-sunset-backlog/2026-07-27/SHARED_CONSUMPTION_PROJECTION_CATALOG.xlsx
+++ b/reports/module-migration-sunset-backlog/2026-07-27/SHARED_CONSUMPTION_PROJECTION_CATALOG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projection Catalog" sheetId="1" r:id="R31fa4b9a4ac0429c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projection Catalog" sheetId="1" r:id="Rf4a884395e79481a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -318,6 +318,7 @@
     <x:col min="8" max="8" width="42" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="42" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="42" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
@@ -331,24 +332,27 @@
         <x:v>projection_family</x:v>
       </x:c>
       <x:c r="D1" s="9" t="str">
+        <x:v>catalog_scope</x:v>
+      </x:c>
+      <x:c r="E1" s="9" t="str">
         <x:v>intended_consumers</x:v>
       </x:c>
-      <x:c r="E1" s="9" t="str">
+      <x:c r="F1" s="9" t="str">
         <x:v>refresh_trigger</x:v>
       </x:c>
-      <x:c r="F1" s="9" t="str">
+      <x:c r="G1" s="9" t="str">
         <x:v>current_authority</x:v>
       </x:c>
-      <x:c r="G1" s="9" t="str">
+      <x:c r="H1" s="9" t="str">
         <x:v>lineage_requirement</x:v>
       </x:c>
-      <x:c r="H1" s="9" t="str">
+      <x:c r="I1" s="9" t="str">
         <x:v>parity_test</x:v>
       </x:c>
-      <x:c r="I1" s="9" t="str">
+      <x:c r="J1" s="9" t="str">
         <x:v>rollback_path</x:v>
       </x:c>
-      <x:c r="J1" s="9" t="str">
+      <x:c r="K1" s="9" t="str">
         <x:v>status</x:v>
       </x:c>
     </x:row>
@@ -363,24 +367,27 @@
         <x:v>consumption.metric_facts</x:v>
       </x:c>
       <x:c r="D2" s="5" t="str">
-        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
+        <x:v>Current discovered persisted-object projection candidate only; Source and Moves target projections belong to the later Module Integration Target Plan</x:v>
       </x:c>
       <x:c r="E2" s="5" t="str">
-        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
+        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
       </x:c>
       <x:c r="F2" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
       </x:c>
       <x:c r="G2" s="5" t="str">
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+      </x:c>
+      <x:c r="H2" s="5" t="str">
         <x:v>value_source; confidence; source_key; source_row</x:v>
       </x:c>
-      <x:c r="H2" s="5" t="str">
-        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
-      </x:c>
       <x:c r="I2" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
       </x:c>
       <x:c r="J2" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="K2" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -395,24 +402,27 @@
         <x:v>consumption.mart_ai_portfolio</x:v>
       </x:c>
       <x:c r="D3" s="5" t="str">
-        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
+        <x:v>Current discovered persisted-object projection candidate only; Source and Moves target projections belong to the later Module Integration Target Plan</x:v>
       </x:c>
       <x:c r="E3" s="5" t="str">
-        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
+        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
       </x:c>
       <x:c r="F3" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
       </x:c>
       <x:c r="G3" s="5" t="str">
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+      </x:c>
+      <x:c r="H3" s="5" t="str">
         <x:v>evidence_ids; source_fact_keys; source_file; source_row</x:v>
       </x:c>
-      <x:c r="H3" s="5" t="str">
-        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
-      </x:c>
       <x:c r="I3" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
       </x:c>
       <x:c r="J3" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="K3" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -427,24 +437,27 @@
         <x:v>consumption.mart_command_center</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
-        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
+        <x:v>Current discovered persisted-object projection candidate only; Source and Moves target projections belong to the later Module Integration Target Plan</x:v>
       </x:c>
       <x:c r="E4" s="5" t="str">
-        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
+        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
       </x:c>
       <x:c r="F4" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
       </x:c>
       <x:c r="G4" s="5" t="str">
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+      </x:c>
+      <x:c r="H4" s="5" t="str">
         <x:v>source_standard; source_run_id; source_fact_keys; source_files</x:v>
       </x:c>
-      <x:c r="H4" s="5" t="str">
-        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
-      </x:c>
       <x:c r="I4" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
       </x:c>
       <x:c r="J4" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="K4" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -459,24 +472,27 @@
         <x:v>consumption.mart_cxo_actions</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
-        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
+        <x:v>Current discovered persisted-object projection candidate only; Source and Moves target projections belong to the later Module Integration Target Plan</x:v>
       </x:c>
       <x:c r="E5" s="5" t="str">
-        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
+        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
       </x:c>
       <x:c r="F5" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
       </x:c>
       <x:c r="G5" s="5" t="str">
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+      </x:c>
+      <x:c r="H5" s="5" t="str">
         <x:v>evidence_ids; source_fact_keys</x:v>
       </x:c>
-      <x:c r="H5" s="5" t="str">
-        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
-      </x:c>
       <x:c r="I5" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
       </x:c>
       <x:c r="J5" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="K5" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -491,24 +507,27 @@
         <x:v>consumption.evidence_mart_evidence_lineage</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
-        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
+        <x:v>Current discovered persisted-object projection candidate only; Source and Moves target projections belong to the later Module Integration Target Plan</x:v>
       </x:c>
       <x:c r="E6" s="5" t="str">
-        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
+        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
       </x:c>
       <x:c r="F6" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
       </x:c>
       <x:c r="G6" s="5" t="str">
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+      </x:c>
+      <x:c r="H6" s="5" t="str">
         <x:v>lineage_key; source_file; source_row; source_system; source_fact_keys</x:v>
       </x:c>
-      <x:c r="H6" s="5" t="str">
-        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
-      </x:c>
       <x:c r="I6" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
       </x:c>
       <x:c r="J6" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="K6" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -523,24 +542,27 @@
         <x:v>consumption.program_mart_program_decision_lanes</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
-        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
+        <x:v>Current discovered persisted-object projection candidate only; Source and Moves target projections belong to the later Module Integration Target Plan</x:v>
       </x:c>
       <x:c r="E7" s="5" t="str">
-        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
+        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
       </x:c>
       <x:c r="F7" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
       </x:c>
       <x:c r="G7" s="5" t="str">
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+      </x:c>
+      <x:c r="H7" s="5" t="str">
         <x:v>evidence_ids; source_fact_keys; source_file; source_row</x:v>
       </x:c>
-      <x:c r="H7" s="5" t="str">
-        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
-      </x:c>
       <x:c r="I7" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
       </x:c>
       <x:c r="J7" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="K7" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -555,24 +577,27 @@
         <x:v>consumption.mart_required_field_gaps</x:v>
       </x:c>
       <x:c r="D8" s="5" t="str">
-        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
+        <x:v>Current discovered persisted-object projection candidate only; Source and Moves target projections belong to the later Module Integration Target Plan</x:v>
       </x:c>
       <x:c r="E8" s="5" t="str">
-        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
+        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
       </x:c>
       <x:c r="F8" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
       </x:c>
       <x:c r="G8" s="5" t="str">
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+      </x:c>
+      <x:c r="H8" s="5" t="str">
         <x:v>source_template; source_record_id</x:v>
       </x:c>
-      <x:c r="H8" s="5" t="str">
-        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
-      </x:c>
       <x:c r="I8" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
       </x:c>
       <x:c r="J8" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="K8" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -584,27 +609,30 @@
         <x:v>cio_tower.mart_value_funnel</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
-        <x:v>consumption.metric_mart_value_funnel</x:v>
+        <x:v>consumption.mart_value_funnel</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
-        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
+        <x:v>Current discovered persisted-object projection candidate only; Source and Moves target projections belong to the later Module Integration Target Plan</x:v>
       </x:c>
       <x:c r="E9" s="5" t="str">
-        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
+        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
       </x:c>
       <x:c r="F9" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
       </x:c>
       <x:c r="G9" s="5" t="str">
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+      </x:c>
+      <x:c r="H9" s="5" t="str">
         <x:v>source_fact_keys; source_file; source_row</x:v>
       </x:c>
-      <x:c r="H9" s="5" t="str">
-        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
-      </x:c>
       <x:c r="I9" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
       </x:c>
       <x:c r="J9" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="K9" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -619,24 +647,27 @@
         <x:v>consumption.metric_measure_results</x:v>
       </x:c>
       <x:c r="D10" s="5" t="str">
-        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
+        <x:v>Current discovered persisted-object projection candidate only; Source and Moves target projections belong to the later Module Integration Target Plan</x:v>
       </x:c>
       <x:c r="E10" s="5" t="str">
-        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
+        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
       </x:c>
       <x:c r="F10" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
       </x:c>
       <x:c r="G10" s="5" t="str">
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+      </x:c>
+      <x:c r="H10" s="5" t="str">
         <x:v>source_fact_keys</x:v>
       </x:c>
-      <x:c r="H10" s="5" t="str">
-        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
-      </x:c>
       <x:c r="I10" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
       </x:c>
       <x:c r="J10" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="K10" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -651,24 +682,27 @@
         <x:v>consumption.context_ai_control_atlas_context_packs</x:v>
       </x:c>
       <x:c r="D11" s="5" t="str">
-        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
+        <x:v>Current discovered persisted-object projection candidate only; Source and Moves target projections belong to the later Module Integration Target Plan</x:v>
       </x:c>
       <x:c r="E11" s="5" t="str">
-        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
+        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
       </x:c>
       <x:c r="F11" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
       </x:c>
       <x:c r="G11" s="5" t="str">
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+      </x:c>
+      <x:c r="H11" s="5" t="str">
         <x:v>evidence_keys</x:v>
       </x:c>
-      <x:c r="H11" s="5" t="str">
-        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
-      </x:c>
       <x:c r="I11" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
       </x:c>
       <x:c r="J11" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="K11" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -683,24 +717,27 @@
         <x:v>consumption.ai_control_tower_lens_mv</x:v>
       </x:c>
       <x:c r="D12" s="5" t="str">
-        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
+        <x:v>Current discovered persisted-object projection candidate only; Source and Moves target projections belong to the later Module Integration Target Plan</x:v>
       </x:c>
       <x:c r="E12" s="5" t="str">
-        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
+        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
       </x:c>
       <x:c r="F12" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
       </x:c>
       <x:c r="G12" s="5" t="str">
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+      </x:c>
+      <x:c r="H12" s="5" t="str">
         <x:v>No parsed lineage fields; inspect write path before promotion</x:v>
       </x:c>
-      <x:c r="H12" s="5" t="str">
-        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
-      </x:c>
       <x:c r="I12" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
       </x:c>
       <x:c r="J12" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="K12" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -715,24 +752,27 @@
         <x:v>consumption.tower_budget_rollups</x:v>
       </x:c>
       <x:c r="D13" s="5" t="str">
-        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
+        <x:v>Current discovered persisted-object projection candidate only; Source and Moves target projections belong to the later Module Integration Target Plan</x:v>
       </x:c>
       <x:c r="E13" s="5" t="str">
-        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
+        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
       </x:c>
       <x:c r="F13" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
       </x:c>
       <x:c r="G13" s="5" t="str">
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+      </x:c>
+      <x:c r="H13" s="5" t="str">
         <x:v>source_file; lineage</x:v>
       </x:c>
-      <x:c r="H13" s="5" t="str">
-        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
-      </x:c>
       <x:c r="I13" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
       </x:c>
       <x:c r="J13" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="K13" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -747,24 +787,27 @@
         <x:v>consumption.relationship_tower_cmdb_dependencies</x:v>
       </x:c>
       <x:c r="D14" s="5" t="str">
-        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
+        <x:v>Current discovered persisted-object projection candidate only; Source and Moves target projections belong to the later Module Integration Target Plan</x:v>
       </x:c>
       <x:c r="E14" s="5" t="str">
-        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
+        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
       </x:c>
       <x:c r="F14" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
       </x:c>
       <x:c r="G14" s="5" t="str">
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+      </x:c>
+      <x:c r="H14" s="5" t="str">
         <x:v>source_ci_sys_id; source_system</x:v>
       </x:c>
-      <x:c r="H14" s="5" t="str">
-        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
-      </x:c>
       <x:c r="I14" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
       </x:c>
       <x:c r="J14" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="K14" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -779,24 +822,27 @@
         <x:v>consumption.metric_tower_dora_metrics</x:v>
       </x:c>
       <x:c r="D15" s="5" t="str">
-        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
+        <x:v>Current discovered persisted-object projection candidate only; Source and Moves target projections belong to the later Module Integration Target Plan</x:v>
       </x:c>
       <x:c r="E15" s="5" t="str">
-        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
+        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
       </x:c>
       <x:c r="F15" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
       </x:c>
       <x:c r="G15" s="5" t="str">
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+      </x:c>
+      <x:c r="H15" s="5" t="str">
         <x:v>source; source_file_id</x:v>
       </x:c>
-      <x:c r="H15" s="5" t="str">
-        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
-      </x:c>
       <x:c r="I15" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
       </x:c>
       <x:c r="J15" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="K15" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -811,24 +857,27 @@
         <x:v>consumption.metric_tower_program_financials</x:v>
       </x:c>
       <x:c r="D16" s="5" t="str">
-        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
+        <x:v>Current discovered persisted-object projection candidate only; Source and Moves target projections belong to the later Module Integration Target Plan</x:v>
       </x:c>
       <x:c r="E16" s="5" t="str">
-        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
+        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
       </x:c>
       <x:c r="F16" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
       </x:c>
       <x:c r="G16" s="5" t="str">
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+      </x:c>
+      <x:c r="H16" s="5" t="str">
         <x:v>source; source_file_id; source_system</x:v>
       </x:c>
-      <x:c r="H16" s="5" t="str">
-        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
-      </x:c>
       <x:c r="I16" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
       </x:c>
       <x:c r="J16" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="K16" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -843,24 +892,27 @@
         <x:v>consumption.metric_tower_vendor_spend</x:v>
       </x:c>
       <x:c r="D17" s="6" t="str">
-        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
+        <x:v>Current discovered persisted-object projection candidate only; Source and Moves target projections belong to the later Module Integration Target Plan</x:v>
       </x:c>
       <x:c r="E17" s="6" t="str">
-        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
+        <x:v>Nexus; aVa; Cube; Superset; Observable; module dashboards; exports</x:v>
       </x:c>
       <x:c r="F17" s="6" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>Domain publication/outbox or controlled materialization run after source reconciliation</x:v>
       </x:c>
       <x:c r="G17" s="6" t="str">
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+      </x:c>
+      <x:c r="H17" s="6" t="str">
         <x:v>source; source_file_id; source_system</x:v>
       </x:c>
-      <x:c r="H17" s="6" t="str">
-        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
-      </x:c>
       <x:c r="I17" s="6" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Compare current screen/API/export answer to new projection output under same tenant and period</x:v>
       </x:c>
       <x:c r="J17" s="6" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="K17" s="6" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
